--- a/n1_lyrica_v2.xlsx
+++ b/n1_lyrica_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70ed252595cc6131/Anexos/stats/teixeira/lyrica/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{B27AD87D-98AD-422C-B062-FEDF74E54619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{992AF75D-938C-474E-A9C2-FA6E2E1B095B}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{B27AD87D-98AD-422C-B062-FEDF74E54619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8119DB5-5C34-4C80-A1F5-76FA1EC6254B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11040" xr2:uid="{94362CDF-6C5D-4417-A2BE-F689EA0486F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="33">
   <si>
     <t>date</t>
   </si>
@@ -130,6 +130,12 @@
   </si>
   <si>
     <t>day2</t>
+  </si>
+  <si>
+    <t>obs_order_cycle</t>
+  </si>
+  <si>
+    <t>obs_order_period</t>
   </si>
 </sst>
 </file>
@@ -202,18 +208,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}" name="Tabela1" displayName="Tabela1" ref="A1:V41" totalsRowShown="0">
-  <autoFilter ref="A1:V41" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}" name="Tabela1" displayName="Tabela1" ref="A1:X46" totalsRowShown="0">
+  <autoFilter ref="A1:X46" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W41">
     <sortCondition ref="C1:C41"/>
   </sortState>
-  <tableColumns count="22">
+  <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{EEFBEE00-D493-40DC-92D6-AFFA40239080}" name="date" dataDxfId="1"/>
     <tableColumn id="16" xr3:uid="{30BAF7A3-909A-4E28-8020-B684EAE0D7D1}" name="d" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{77CAD242-3C2D-4EED-8D68-00E184EC9C43}" name="day"/>
     <tableColumn id="3" xr3:uid="{4E3C930C-8192-4A04-BA00-DCBC655547D0}" name="cycle"/>
     <tableColumn id="4" xr3:uid="{C56B3168-3BA9-4F60-91F2-D557C3684C2C}" name="treat"/>
     <tableColumn id="5" xr3:uid="{6734E705-8671-42EF-855D-BC4733B04E2F}" name="order"/>
+    <tableColumn id="17" xr3:uid="{95763741-DE4C-453F-A01E-5E957C1DBC30}" name="obs_order_period"/>
+    <tableColumn id="18" xr3:uid="{C2AE19BE-585D-4C53-B7D0-4DF7E3AA34D5}" name="obs_order_cycle"/>
     <tableColumn id="19" xr3:uid="{7B4C7719-06F8-4615-91D6-BF72E2583EF8}" name="eye_pain_morn"/>
     <tableColumn id="6" xr3:uid="{7EE843D3-7FF3-4793-8A08-78286A8352EA}" name="sleep_ordinal"/>
     <tableColumn id="7" xr3:uid="{D2CD69ED-9DE9-457B-92AC-8E035CF687C7}" name="sleep_cont"/>
@@ -532,22 +540,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D88D48-57DE-49F5-B1C2-4D6C6D40FFB9}">
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="6.7109375" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" customWidth="1"/>
     <col min="4" max="4" width="6.140625" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" customWidth="1"/>
-    <col min="7" max="14" width="8.7109375" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" customWidth="1"/>
-    <col min="16" max="19" width="8.42578125" customWidth="1"/>
-    <col min="20" max="22" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="8" width="7.42578125" customWidth="1"/>
+    <col min="9" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.140625" customWidth="1"/>
+    <col min="18" max="21" width="8.42578125" customWidth="1"/>
+    <col min="22" max="24" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,55 +575,61 @@
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45966</v>
       </c>
@@ -635,37 +649,43 @@
         <v>1</v>
       </c>
       <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>28</v>
       </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>25</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>30</v>
       </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-      <c r="N2">
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
         <v>29</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>25</v>
       </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="T2" t="s">
-        <v>20</v>
-      </c>
-      <c r="V2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="V2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45967</v>
       </c>
@@ -685,43 +705,49 @@
         <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>22</v>
       </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
         <v>32</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>28</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>10</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>18</v>
       </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-      <c r="N3">
+      <c r="O3">
+        <v>2</v>
+      </c>
+      <c r="P3">
         <v>22</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>31</v>
       </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="T3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="V3" t="s">
+        <v>20</v>
+      </c>
+      <c r="X3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45968</v>
       </c>
@@ -741,40 +767,46 @@
         <v>1</v>
       </c>
       <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>28</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <v>18</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>22</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>10</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>16</v>
       </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-      <c r="N4">
-        <v>20</v>
-      </c>
       <c r="O4">
+        <v>2</v>
+      </c>
+      <c r="P4">
+        <v>20</v>
+      </c>
+      <c r="Q4">
         <v>32</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>0</v>
       </c>
-      <c r="V4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45969</v>
       </c>
@@ -794,43 +826,49 @@
         <v>1</v>
       </c>
       <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
         <v>23</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
         <v>38</v>
       </c>
-      <c r="J5">
-        <v>20</v>
-      </c>
-      <c r="K5">
+      <c r="L5">
+        <v>20</v>
+      </c>
+      <c r="M5">
         <v>10</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>14</v>
       </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-      <c r="N5">
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
         <v>24</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>27</v>
       </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="T5" t="s">
-        <v>20</v>
-      </c>
-      <c r="V5">
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="V5" t="s">
+        <v>20</v>
+      </c>
+      <c r="X5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45970</v>
       </c>
@@ -850,37 +888,43 @@
         <v>1</v>
       </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
         <v>18</v>
       </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
         <v>24</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>25</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>9.75</v>
       </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-      <c r="N6">
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
         <v>23</v>
       </c>
-      <c r="O6">
-        <v>20</v>
-      </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>20</v>
+      </c>
+      <c r="R6">
         <v>0</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45980</v>
       </c>
@@ -900,43 +944,49 @@
         <v>2</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
         <v>21</v>
       </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
         <v>18</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>35</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>8.5</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>14</v>
       </c>
-      <c r="M7">
-        <v>2</v>
-      </c>
-      <c r="N7">
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7">
         <v>24</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>28</v>
       </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="W7" t="s">
         <v>22</v>
       </c>
-      <c r="V7">
+      <c r="X7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45981</v>
       </c>
@@ -956,40 +1006,46 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
         <v>23</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>28</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>9.5</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>15</v>
       </c>
-      <c r="M8">
-        <v>2</v>
-      </c>
-      <c r="N8">
+      <c r="O8">
+        <v>2</v>
+      </c>
+      <c r="P8">
         <v>27</v>
       </c>
-      <c r="O8">
+      <c r="Q8">
         <v>23</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>0</v>
       </c>
-      <c r="V8">
+      <c r="X8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45982</v>
       </c>
@@ -1009,40 +1065,46 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I9">
+        <v>20</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
         <v>29</v>
       </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
+      <c r="L9">
+        <v>20</v>
+      </c>
+      <c r="M9">
         <v>9.6999999999999993</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>15</v>
       </c>
-      <c r="M9">
-        <v>2</v>
-      </c>
-      <c r="N9">
+      <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
         <v>23</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>24</v>
       </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="V9">
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="X9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45983</v>
       </c>
@@ -1062,37 +1124,43 @@
         <v>2</v>
       </c>
       <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>9</v>
+      </c>
+      <c r="I10">
         <v>25</v>
       </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
-      <c r="I10">
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
         <v>35</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>24</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>11.5</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>16</v>
       </c>
-      <c r="M10">
-        <v>2</v>
-      </c>
-      <c r="N10">
+      <c r="O10">
+        <v>2</v>
+      </c>
+      <c r="P10">
         <v>25</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>30</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45984</v>
       </c>
@@ -1112,40 +1180,46 @@
         <v>2</v>
       </c>
       <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>10</v>
+      </c>
+      <c r="I11">
         <v>25</v>
       </c>
-      <c r="H11">
-        <v>3</v>
-      </c>
-      <c r="I11">
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
         <v>36</v>
       </c>
-      <c r="J11">
-        <v>20</v>
-      </c>
-      <c r="K11">
+      <c r="L11">
+        <v>20</v>
+      </c>
+      <c r="M11">
         <v>12</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>14</v>
       </c>
-      <c r="M11">
-        <v>2</v>
-      </c>
-      <c r="N11">
+      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="P11">
         <v>22</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>26</v>
       </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="V11">
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="X11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45994</v>
       </c>
@@ -1165,40 +1239,46 @@
         <v>1</v>
       </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>22</v>
       </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-      <c r="I12">
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
         <v>24</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>33</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>10.5</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>14</v>
       </c>
-      <c r="M12">
-        <v>2</v>
-      </c>
-      <c r="N12">
+      <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12">
         <v>22</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>27</v>
       </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="V12">
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="X12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45995</v>
       </c>
@@ -1218,40 +1298,46 @@
         <v>1</v>
       </c>
       <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
         <v>25</v>
       </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-      <c r="I13">
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
         <v>22</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>35</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>10.6</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>14</v>
       </c>
-      <c r="M13">
-        <v>2</v>
-      </c>
-      <c r="N13">
-        <v>20</v>
-      </c>
       <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>20</v>
+      </c>
+      <c r="Q13">
         <v>26</v>
       </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="V13">
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="X13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45996</v>
       </c>
@@ -1271,43 +1357,49 @@
         <v>1</v>
       </c>
       <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
         <v>25</v>
       </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-      <c r="I14">
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
         <v>16</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>30</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>10.8</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>14</v>
       </c>
-      <c r="M14">
-        <v>2</v>
-      </c>
-      <c r="N14">
-        <v>20</v>
-      </c>
       <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>20</v>
+      </c>
+      <c r="Q14">
         <v>25</v>
       </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="U14" t="s">
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="W14" t="s">
         <v>23</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45997</v>
       </c>
@@ -1327,40 +1419,46 @@
         <v>1</v>
       </c>
       <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15">
         <v>24</v>
       </c>
-      <c r="H15">
-        <v>3</v>
-      </c>
-      <c r="I15">
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
         <v>33</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>33</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>10.9</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>14</v>
       </c>
-      <c r="M15">
-        <v>2</v>
-      </c>
-      <c r="N15">
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
         <v>22</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>26</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>0</v>
       </c>
-      <c r="V15">
+      <c r="X15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45998</v>
       </c>
@@ -1380,40 +1478,46 @@
         <v>1</v>
       </c>
       <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
         <v>24</v>
       </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-      <c r="I16">
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
         <v>25</v>
       </c>
-      <c r="J16">
-        <v>20</v>
-      </c>
-      <c r="K16">
+      <c r="L16">
+        <v>20</v>
+      </c>
+      <c r="M16">
         <v>10.8</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>14</v>
       </c>
-      <c r="M16">
-        <v>3</v>
-      </c>
-      <c r="N16">
+      <c r="O16">
+        <v>3</v>
+      </c>
+      <c r="P16">
         <v>35</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>30</v>
       </c>
-      <c r="P16">
-        <v>1</v>
-      </c>
-      <c r="V16">
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="X16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46008</v>
       </c>
@@ -1433,37 +1537,43 @@
         <v>2</v>
       </c>
       <c r="G17">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I17">
+        <v>20</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
         <v>18</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>25</v>
       </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
-      <c r="N17">
+      <c r="O17">
+        <v>2</v>
+      </c>
+      <c r="P17">
         <v>25</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>25</v>
       </c>
-      <c r="P17">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>20</v>
-      </c>
-      <c r="V17">
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17" t="s">
+        <v>20</v>
+      </c>
+      <c r="X17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46009</v>
       </c>
@@ -1483,43 +1593,49 @@
         <v>2</v>
       </c>
       <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>7</v>
+      </c>
+      <c r="I18">
         <v>18</v>
       </c>
-      <c r="H18">
-        <v>3</v>
-      </c>
-      <c r="I18">
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
         <v>36</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>28</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>9</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>14</v>
       </c>
-      <c r="M18">
-        <v>3</v>
-      </c>
-      <c r="N18">
+      <c r="O18">
+        <v>3</v>
+      </c>
+      <c r="P18">
         <v>33</v>
       </c>
-      <c r="O18">
+      <c r="Q18">
         <v>29</v>
       </c>
-      <c r="P18">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>20</v>
-      </c>
-      <c r="V18">
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18" t="s">
+        <v>20</v>
+      </c>
+      <c r="X18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46010</v>
       </c>
@@ -1539,43 +1655,49 @@
         <v>2</v>
       </c>
       <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>8</v>
+      </c>
+      <c r="I19">
         <v>24</v>
       </c>
-      <c r="H19">
-        <v>3</v>
-      </c>
-      <c r="I19">
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19">
         <v>30</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>38</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>4</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>38</v>
       </c>
-      <c r="O19">
+      <c r="Q19">
         <v>35</v>
       </c>
-      <c r="P19">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>20</v>
-      </c>
-      <c r="T19" t="s">
-        <v>20</v>
-      </c>
-      <c r="U19" t="s">
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19" t="s">
+        <v>20</v>
+      </c>
+      <c r="V19" t="s">
+        <v>20</v>
+      </c>
+      <c r="W19" t="s">
         <v>24</v>
       </c>
-      <c r="V19">
+      <c r="X19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46011</v>
       </c>
@@ -1595,43 +1717,49 @@
         <v>2</v>
       </c>
       <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>9</v>
+      </c>
+      <c r="I20">
         <v>25</v>
       </c>
-      <c r="H20">
-        <v>3</v>
-      </c>
-      <c r="I20">
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
         <v>26</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>22</v>
       </c>
-      <c r="K20">
+      <c r="M20">
         <v>9.75</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>14</v>
       </c>
-      <c r="M20">
-        <v>3</v>
-      </c>
-      <c r="N20">
+      <c r="O20">
+        <v>3</v>
+      </c>
+      <c r="P20">
         <v>32</v>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>35</v>
       </c>
-      <c r="P20">
+      <c r="R20">
         <v>0</v>
       </c>
-      <c r="Q20" t="s">
-        <v>20</v>
-      </c>
-      <c r="V20">
+      <c r="S20" t="s">
+        <v>20</v>
+      </c>
+      <c r="X20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46012</v>
       </c>
@@ -1651,43 +1779,49 @@
         <v>2</v>
       </c>
       <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+      <c r="I21">
         <v>19</v>
       </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
-      <c r="I21">
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
         <v>22</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>27</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>10</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>15</v>
       </c>
-      <c r="M21">
-        <v>3</v>
-      </c>
-      <c r="N21">
+      <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21">
         <v>34</v>
       </c>
-      <c r="O21">
+      <c r="Q21">
         <v>32</v>
       </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>20</v>
-      </c>
-      <c r="V21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21" t="s">
+        <v>20</v>
+      </c>
+      <c r="X21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46022</v>
       </c>
@@ -1707,37 +1841,43 @@
         <v>1</v>
       </c>
       <c r="G22">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>22</v>
       </c>
       <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>22</v>
+      </c>
+      <c r="L22">
         <v>30</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>10</v>
       </c>
-      <c r="M22">
-        <v>3</v>
-      </c>
-      <c r="N22">
+      <c r="O22">
+        <v>3</v>
+      </c>
+      <c r="P22">
         <v>33</v>
       </c>
-      <c r="O22">
+      <c r="Q22">
         <v>22</v>
       </c>
-      <c r="P22">
-        <v>1</v>
-      </c>
-      <c r="V22">
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="X22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46023</v>
       </c>
@@ -1757,37 +1897,43 @@
         <v>1</v>
       </c>
       <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
         <v>27</v>
       </c>
-      <c r="H23">
-        <v>3</v>
-      </c>
-      <c r="I23">
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
         <v>29</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>26</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>10.5</v>
       </c>
-      <c r="M23">
-        <v>2</v>
-      </c>
-      <c r="N23">
+      <c r="O23">
+        <v>2</v>
+      </c>
+      <c r="P23">
         <v>24</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
         <v>25</v>
       </c>
-      <c r="P23">
-        <v>1</v>
-      </c>
-      <c r="V23">
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="X23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46024</v>
       </c>
@@ -1807,43 +1953,49 @@
         <v>1</v>
       </c>
       <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
         <v>28</v>
       </c>
-      <c r="H24">
-        <v>3</v>
-      </c>
-      <c r="I24">
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24">
         <v>27</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>26</v>
       </c>
-      <c r="M24">
-        <v>2</v>
-      </c>
-      <c r="N24">
+      <c r="O24">
+        <v>2</v>
+      </c>
+      <c r="P24">
         <v>26</v>
       </c>
-      <c r="O24">
+      <c r="Q24">
         <v>30</v>
       </c>
-      <c r="P24">
+      <c r="R24">
         <v>0</v>
       </c>
-      <c r="Q24" t="s">
-        <v>20</v>
-      </c>
-      <c r="R24" t="s">
-        <v>20</v>
-      </c>
       <c r="S24" t="s">
         <v>20</v>
       </c>
-      <c r="V24">
+      <c r="T24" t="s">
+        <v>20</v>
+      </c>
+      <c r="U24" t="s">
+        <v>20</v>
+      </c>
+      <c r="X24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46025</v>
       </c>
@@ -1863,49 +2015,55 @@
         <v>1</v>
       </c>
       <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25">
+        <v>4</v>
+      </c>
+      <c r="I25">
         <v>25</v>
       </c>
-      <c r="H25">
-        <v>3</v>
-      </c>
-      <c r="I25">
+      <c r="J25">
+        <v>3</v>
+      </c>
+      <c r="K25">
         <v>29</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>28</v>
       </c>
-      <c r="K25">
+      <c r="M25">
         <v>10</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>21</v>
       </c>
-      <c r="M25">
-        <v>3</v>
-      </c>
-      <c r="N25">
+      <c r="O25">
+        <v>3</v>
+      </c>
+      <c r="P25">
         <v>30</v>
       </c>
-      <c r="O25">
+      <c r="Q25">
         <v>32</v>
       </c>
-      <c r="P25">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>20</v>
-      </c>
-      <c r="R25" t="s">
-        <v>20</v>
+      <c r="R25">
+        <v>1</v>
       </c>
       <c r="S25" t="s">
         <v>20</v>
       </c>
-      <c r="V25">
+      <c r="T25" t="s">
+        <v>20</v>
+      </c>
+      <c r="U25" t="s">
+        <v>20</v>
+      </c>
+      <c r="X25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46026</v>
       </c>
@@ -1925,46 +2083,52 @@
         <v>1</v>
       </c>
       <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26">
+        <v>5</v>
+      </c>
+      <c r="I26">
         <v>24</v>
       </c>
-      <c r="H26">
-        <v>3</v>
-      </c>
-      <c r="I26">
+      <c r="J26">
+        <v>3</v>
+      </c>
+      <c r="K26">
         <v>30</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>30</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>21</v>
       </c>
-      <c r="M26">
-        <v>3</v>
-      </c>
-      <c r="N26">
+      <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="P26">
         <v>33</v>
       </c>
-      <c r="O26">
+      <c r="Q26">
         <v>29</v>
       </c>
-      <c r="P26">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>20</v>
-      </c>
-      <c r="R26" t="s">
-        <v>20</v>
+      <c r="R26">
+        <v>1</v>
       </c>
       <c r="S26" t="s">
         <v>20</v>
       </c>
-      <c r="V26">
+      <c r="T26" t="s">
+        <v>20</v>
+      </c>
+      <c r="U26" t="s">
+        <v>20</v>
+      </c>
+      <c r="X26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46036</v>
       </c>
@@ -1984,43 +2148,49 @@
         <v>2</v>
       </c>
       <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>6</v>
+      </c>
+      <c r="I27">
         <v>25</v>
       </c>
-      <c r="H27">
-        <v>3</v>
-      </c>
-      <c r="I27">
+      <c r="J27">
+        <v>3</v>
+      </c>
+      <c r="K27">
         <v>26</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>28</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>10.5</v>
       </c>
-      <c r="L27">
-        <v>20</v>
-      </c>
-      <c r="M27">
-        <v>2</v>
-      </c>
       <c r="N27">
+        <v>20</v>
+      </c>
+      <c r="O27">
+        <v>2</v>
+      </c>
+      <c r="P27">
         <v>25</v>
       </c>
-      <c r="O27">
+      <c r="Q27">
         <v>28</v>
       </c>
-      <c r="P27">
-        <v>1</v>
-      </c>
-      <c r="R27" t="s">
-        <v>20</v>
-      </c>
-      <c r="V27">
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="T27" t="s">
+        <v>20</v>
+      </c>
+      <c r="X27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46037</v>
       </c>
@@ -2040,43 +2210,49 @@
         <v>2</v>
       </c>
       <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>7</v>
+      </c>
+      <c r="I28">
         <v>21</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>4</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>38</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>27</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>10</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>21</v>
       </c>
-      <c r="M28">
-        <v>3</v>
-      </c>
-      <c r="N28">
+      <c r="O28">
+        <v>3</v>
+      </c>
+      <c r="P28">
         <v>26</v>
       </c>
-      <c r="O28">
+      <c r="Q28">
         <v>28</v>
       </c>
-      <c r="P28">
-        <v>1</v>
-      </c>
-      <c r="R28" t="s">
-        <v>20</v>
-      </c>
-      <c r="V28">
+      <c r="R28">
+        <v>1</v>
+      </c>
+      <c r="T28" t="s">
+        <v>20</v>
+      </c>
+      <c r="X28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46038</v>
       </c>
@@ -2096,40 +2272,46 @@
         <v>2</v>
       </c>
       <c r="G29">
+        <v>3</v>
+      </c>
+      <c r="H29">
+        <v>8</v>
+      </c>
+      <c r="I29">
         <v>23</v>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>4</v>
       </c>
-      <c r="I29">
+      <c r="K29">
         <v>36</v>
       </c>
-      <c r="J29">
+      <c r="L29">
         <v>26</v>
       </c>
-      <c r="L29">
+      <c r="N29">
         <v>21</v>
       </c>
-      <c r="M29">
-        <v>2</v>
-      </c>
-      <c r="N29">
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29">
         <v>23</v>
       </c>
-      <c r="O29">
+      <c r="Q29">
         <v>26</v>
       </c>
-      <c r="P29">
-        <v>1</v>
-      </c>
-      <c r="R29" t="s">
-        <v>20</v>
-      </c>
-      <c r="V29">
+      <c r="R29">
+        <v>1</v>
+      </c>
+      <c r="T29" t="s">
+        <v>20</v>
+      </c>
+      <c r="X29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46039</v>
       </c>
@@ -2149,37 +2331,43 @@
         <v>2</v>
       </c>
       <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>9</v>
+      </c>
+      <c r="I30">
         <v>23</v>
       </c>
-      <c r="H30">
-        <v>3</v>
-      </c>
-      <c r="I30">
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
         <v>33</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>22</v>
       </c>
-      <c r="K30">
+      <c r="M30">
         <v>9.5</v>
       </c>
-      <c r="M30">
-        <v>3</v>
-      </c>
-      <c r="N30">
+      <c r="O30">
+        <v>3</v>
+      </c>
+      <c r="P30">
         <v>26</v>
       </c>
-      <c r="O30">
+      <c r="Q30">
         <v>28</v>
       </c>
-      <c r="P30">
+      <c r="R30">
         <v>0</v>
       </c>
-      <c r="V30">
+      <c r="X30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46040</v>
       </c>
@@ -2199,37 +2387,43 @@
         <v>2</v>
       </c>
       <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31">
+        <v>10</v>
+      </c>
+      <c r="I31">
         <v>22</v>
       </c>
-      <c r="H31">
-        <v>3</v>
-      </c>
-      <c r="I31">
+      <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31">
         <v>29</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>30</v>
       </c>
-      <c r="K31">
+      <c r="M31">
         <v>10.5</v>
       </c>
-      <c r="M31">
-        <v>3</v>
-      </c>
-      <c r="N31">
+      <c r="O31">
+        <v>3</v>
+      </c>
+      <c r="P31">
         <v>30</v>
       </c>
-      <c r="O31">
+      <c r="Q31">
         <v>29</v>
       </c>
-      <c r="P31">
-        <v>1</v>
-      </c>
-      <c r="V31">
+      <c r="R31">
+        <v>1</v>
+      </c>
+      <c r="X31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46050</v>
       </c>
@@ -2249,40 +2443,46 @@
         <v>1</v>
       </c>
       <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
         <v>31</v>
       </c>
-      <c r="H32">
+      <c r="J32">
         <v>5</v>
       </c>
-      <c r="I32">
+      <c r="K32">
         <v>50</v>
       </c>
-      <c r="J32">
+      <c r="L32">
         <v>30</v>
       </c>
-      <c r="L32">
+      <c r="N32">
         <v>19</v>
       </c>
-      <c r="M32">
-        <v>2</v>
-      </c>
-      <c r="N32">
+      <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="P32">
         <v>24</v>
       </c>
-      <c r="O32">
+      <c r="Q32">
         <v>28</v>
       </c>
-      <c r="P32">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>20</v>
-      </c>
-      <c r="V32">
+      <c r="R32">
+        <v>1</v>
+      </c>
+      <c r="S32" t="s">
+        <v>20</v>
+      </c>
+      <c r="X32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46051</v>
       </c>
@@ -2302,40 +2502,46 @@
         <v>1</v>
       </c>
       <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
         <v>27</v>
       </c>
-      <c r="H33">
-        <v>3</v>
-      </c>
-      <c r="I33">
+      <c r="J33">
+        <v>3</v>
+      </c>
+      <c r="K33">
         <v>34</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>27</v>
       </c>
-      <c r="L33">
-        <v>20</v>
-      </c>
-      <c r="M33">
-        <v>3</v>
-      </c>
       <c r="N33">
+        <v>20</v>
+      </c>
+      <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="P33">
         <v>28</v>
       </c>
-      <c r="O33">
+      <c r="Q33">
         <v>30</v>
       </c>
-      <c r="P33">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>20</v>
-      </c>
-      <c r="V33">
+      <c r="R33">
+        <v>1</v>
+      </c>
+      <c r="S33" t="s">
+        <v>20</v>
+      </c>
+      <c r="X33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46052</v>
       </c>
@@ -2355,46 +2561,52 @@
         <v>1</v>
       </c>
       <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
         <v>35</v>
       </c>
-      <c r="H34">
-        <v>3</v>
-      </c>
-      <c r="I34">
+      <c r="J34">
+        <v>3</v>
+      </c>
+      <c r="K34">
         <v>26</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>30</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>10</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>21</v>
       </c>
-      <c r="M34">
-        <v>3</v>
-      </c>
-      <c r="N34">
+      <c r="O34">
+        <v>3</v>
+      </c>
+      <c r="P34">
         <v>26</v>
       </c>
-      <c r="O34">
+      <c r="Q34">
         <v>32</v>
       </c>
-      <c r="P34">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>20</v>
-      </c>
-      <c r="R34" t="s">
-        <v>20</v>
-      </c>
-      <c r="V34">
+      <c r="R34">
+        <v>1</v>
+      </c>
+      <c r="S34" t="s">
+        <v>20</v>
+      </c>
+      <c r="T34" t="s">
+        <v>20</v>
+      </c>
+      <c r="X34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46053</v>
       </c>
@@ -2414,34 +2626,40 @@
         <v>1</v>
       </c>
       <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35">
+        <v>4</v>
+      </c>
+      <c r="I35">
         <v>32</v>
       </c>
-      <c r="H35">
-        <v>3</v>
-      </c>
-      <c r="I35">
+      <c r="J35">
+        <v>3</v>
+      </c>
+      <c r="K35">
         <v>34</v>
       </c>
-      <c r="J35">
+      <c r="L35">
         <v>29</v>
       </c>
-      <c r="M35">
-        <v>3</v>
-      </c>
-      <c r="N35">
+      <c r="O35">
+        <v>3</v>
+      </c>
+      <c r="P35">
         <v>28</v>
       </c>
-      <c r="O35">
+      <c r="Q35">
         <v>35</v>
       </c>
-      <c r="P35">
-        <v>1</v>
-      </c>
-      <c r="V35">
+      <c r="R35">
+        <v>1</v>
+      </c>
+      <c r="X35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46054</v>
       </c>
@@ -2461,40 +2679,46 @@
         <v>1</v>
       </c>
       <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36">
+        <v>5</v>
+      </c>
+      <c r="I36">
         <v>30</v>
       </c>
-      <c r="H36">
-        <v>3</v>
-      </c>
-      <c r="I36">
+      <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36">
         <v>29</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>24</v>
       </c>
-      <c r="K36">
+      <c r="M36">
         <v>10.75</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>21</v>
       </c>
-      <c r="M36">
-        <v>2</v>
-      </c>
-      <c r="N36">
+      <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="P36">
         <v>22</v>
       </c>
-      <c r="O36">
+      <c r="Q36">
         <v>33</v>
       </c>
-      <c r="P36">
-        <v>1</v>
-      </c>
-      <c r="V36">
+      <c r="R36">
+        <v>1</v>
+      </c>
+      <c r="X36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46064</v>
       </c>
@@ -2514,40 +2738,46 @@
         <v>2</v>
       </c>
       <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>6</v>
+      </c>
+      <c r="I37">
         <v>25</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>4</v>
       </c>
-      <c r="I37">
+      <c r="K37">
         <v>42</v>
       </c>
-      <c r="J37">
+      <c r="L37">
         <v>33</v>
       </c>
-      <c r="L37">
+      <c r="N37">
         <v>21</v>
       </c>
-      <c r="M37">
-        <v>3</v>
-      </c>
-      <c r="N37">
+      <c r="O37">
+        <v>3</v>
+      </c>
+      <c r="P37">
         <v>29</v>
       </c>
-      <c r="O37">
+      <c r="Q37">
         <v>33</v>
       </c>
-      <c r="P37">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>20</v>
-      </c>
-      <c r="V37">
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37" t="s">
+        <v>20</v>
+      </c>
+      <c r="X37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46065</v>
       </c>
@@ -2567,43 +2797,49 @@
         <v>2</v>
       </c>
       <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>7</v>
+      </c>
+      <c r="I38">
         <v>25</v>
       </c>
-      <c r="H38">
-        <v>3</v>
-      </c>
-      <c r="I38">
+      <c r="J38">
+        <v>3</v>
+      </c>
+      <c r="K38">
         <v>33</v>
       </c>
-      <c r="J38">
+      <c r="L38">
         <v>24</v>
       </c>
-      <c r="K38">
+      <c r="M38">
         <v>9.75</v>
       </c>
-      <c r="L38">
+      <c r="N38">
         <v>21</v>
       </c>
-      <c r="M38">
-        <v>2</v>
-      </c>
-      <c r="N38">
+      <c r="O38">
+        <v>2</v>
+      </c>
+      <c r="P38">
         <v>24</v>
       </c>
-      <c r="O38">
+      <c r="Q38">
         <v>29</v>
       </c>
-      <c r="P38">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>20</v>
-      </c>
-      <c r="V38">
+      <c r="R38">
+        <v>1</v>
+      </c>
+      <c r="S38" t="s">
+        <v>20</v>
+      </c>
+      <c r="X38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46066</v>
       </c>
@@ -2623,34 +2859,40 @@
         <v>2</v>
       </c>
       <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <v>8</v>
+      </c>
+      <c r="I39">
         <v>25</v>
       </c>
-      <c r="H39">
-        <v>2</v>
-      </c>
-      <c r="I39">
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39">
         <v>22</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>22</v>
       </c>
-      <c r="M39">
-        <v>3</v>
-      </c>
-      <c r="N39">
+      <c r="O39">
+        <v>3</v>
+      </c>
+      <c r="P39">
         <v>25</v>
       </c>
-      <c r="O39">
+      <c r="Q39">
         <v>28</v>
       </c>
-      <c r="P39">
-        <v>1</v>
-      </c>
-      <c r="V39">
+      <c r="R39">
+        <v>1</v>
+      </c>
+      <c r="X39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46067</v>
       </c>
@@ -2670,40 +2912,46 @@
         <v>2</v>
       </c>
       <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>9</v>
+      </c>
+      <c r="I40">
         <v>21</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>4</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>36</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>32</v>
       </c>
-      <c r="L40">
+      <c r="N40">
         <v>21</v>
       </c>
-      <c r="M40">
-        <v>2</v>
-      </c>
-      <c r="N40">
+      <c r="O40">
+        <v>2</v>
+      </c>
+      <c r="P40">
         <v>22</v>
       </c>
-      <c r="O40">
+      <c r="Q40">
         <v>28</v>
       </c>
-      <c r="P40">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>20</v>
-      </c>
-      <c r="V40">
+      <c r="R40">
+        <v>1</v>
+      </c>
+      <c r="S40" t="s">
+        <v>20</v>
+      </c>
+      <c r="X40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46068</v>
       </c>
@@ -2723,41 +2971,67 @@
         <v>2</v>
       </c>
       <c r="G41">
+        <v>5</v>
+      </c>
+      <c r="H41">
+        <v>10</v>
+      </c>
+      <c r="I41">
         <v>22</v>
       </c>
-      <c r="H41">
-        <v>3</v>
-      </c>
-      <c r="I41">
+      <c r="J41">
+        <v>3</v>
+      </c>
+      <c r="K41">
         <v>34</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>33</v>
       </c>
-      <c r="K41">
+      <c r="M41">
         <v>10.7</v>
       </c>
-      <c r="L41">
+      <c r="N41">
         <v>21</v>
       </c>
-      <c r="M41">
-        <v>3</v>
-      </c>
-      <c r="N41">
+      <c r="O41">
+        <v>3</v>
+      </c>
+      <c r="P41">
         <v>26</v>
       </c>
-      <c r="O41">
+      <c r="Q41">
         <v>28</v>
       </c>
-      <c r="P41">
-        <v>1</v>
-      </c>
-      <c r="R41" t="s">
-        <v>20</v>
-      </c>
-      <c r="V41">
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="T41" t="s">
+        <v>20</v>
+      </c>
+      <c r="X41">
         <v>40</v>
       </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/n1_lyrica_v2.xlsx
+++ b/n1_lyrica_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70ed252595cc6131/Anexos/stats/teixeira/lyrica/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{B27AD87D-98AD-422C-B062-FEDF74E54619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8119DB5-5C34-4C80-A1F5-76FA1EC6254B}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{B27AD87D-98AD-422C-B062-FEDF74E54619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82B37E32-FFEC-47E7-B775-ADF5405D534B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11040" xr2:uid="{94362CDF-6C5D-4417-A2BE-F689EA0486F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="34">
   <si>
     <t>date</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>obs_order_period</t>
+  </si>
+  <si>
+    <t>period</t>
   </si>
 </sst>
 </file>
@@ -208,17 +211,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}" name="Tabela1" displayName="Tabela1" ref="A1:X46" totalsRowShown="0">
-  <autoFilter ref="A1:X46" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}" name="Tabela1" displayName="Tabela1" ref="A1:Y46" totalsRowShown="0">
+  <autoFilter ref="A1:Y46" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X41">
     <sortCondition ref="C1:C41"/>
   </sortState>
-  <tableColumns count="24">
+  <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{EEFBEE00-D493-40DC-92D6-AFFA40239080}" name="date" dataDxfId="1"/>
     <tableColumn id="16" xr3:uid="{30BAF7A3-909A-4E28-8020-B684EAE0D7D1}" name="d" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{77CAD242-3C2D-4EED-8D68-00E184EC9C43}" name="day"/>
     <tableColumn id="3" xr3:uid="{4E3C930C-8192-4A04-BA00-DCBC655547D0}" name="cycle"/>
     <tableColumn id="4" xr3:uid="{C56B3168-3BA9-4F60-91F2-D557C3684C2C}" name="treat"/>
+    <tableColumn id="25" xr3:uid="{02C42277-A369-462B-AB15-C4EB0FA3499D}" name="period"/>
     <tableColumn id="5" xr3:uid="{6734E705-8671-42EF-855D-BC4733B04E2F}" name="order"/>
     <tableColumn id="17" xr3:uid="{95763741-DE4C-453F-A01E-5E957C1DBC30}" name="obs_order_period"/>
     <tableColumn id="18" xr3:uid="{C2AE19BE-585D-4C53-B7D0-4DF7E3AA34D5}" name="obs_order_cycle"/>
@@ -540,22 +544,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D88D48-57DE-49F5-B1C2-4D6C6D40FFB9}">
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="6.7109375" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" customWidth="1"/>
     <col min="4" max="4" width="6.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="8" width="7.42578125" customWidth="1"/>
-    <col min="9" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.140625" customWidth="1"/>
-    <col min="18" max="21" width="8.42578125" customWidth="1"/>
-    <col min="22" max="24" width="8.7109375" customWidth="1"/>
+    <col min="5" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="9" width="7.42578125" customWidth="1"/>
+    <col min="10" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="18" width="6.140625" customWidth="1"/>
+    <col min="19" max="22" width="8.42578125" customWidth="1"/>
+    <col min="23" max="25" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -572,64 +576,67 @@
         <v>6</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45966</v>
       </c>
@@ -655,37 +662,40 @@
         <v>1</v>
       </c>
       <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>28</v>
       </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
       <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
         <v>25</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>30</v>
       </c>
-      <c r="O2">
-        <v>2</v>
-      </c>
       <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
         <v>29</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>25</v>
       </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="V2" t="s">
-        <v>20</v>
-      </c>
-      <c r="X2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45967</v>
       </c>
@@ -705,49 +715,52 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <v>22</v>
       </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
       <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
         <v>32</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>28</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>10</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>18</v>
       </c>
-      <c r="O3">
-        <v>2</v>
-      </c>
       <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
         <v>22</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>31</v>
       </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="V3" t="s">
-        <v>20</v>
-      </c>
-      <c r="X3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="W3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45968</v>
       </c>
@@ -767,46 +780,49 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
         <v>28</v>
       </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
       <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
         <v>18</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>22</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>10</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>16</v>
       </c>
-      <c r="O4">
-        <v>2</v>
-      </c>
       <c r="P4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q4">
+        <v>20</v>
+      </c>
+      <c r="R4">
         <v>32</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>0</v>
       </c>
-      <c r="X4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45969</v>
       </c>
@@ -826,49 +842,52 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
         <v>23</v>
       </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
       <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
         <v>38</v>
       </c>
-      <c r="L5">
-        <v>20</v>
-      </c>
       <c r="M5">
+        <v>20</v>
+      </c>
+      <c r="N5">
         <v>10</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>14</v>
       </c>
-      <c r="O5">
-        <v>2</v>
-      </c>
       <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
         <v>24</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>27</v>
       </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="V5" t="s">
-        <v>20</v>
-      </c>
-      <c r="X5">
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="W5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45970</v>
       </c>
@@ -888,43 +907,46 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>5</v>
       </c>
       <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
         <v>18</v>
       </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
       <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <v>24</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>25</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>9.75</v>
       </c>
-      <c r="O6">
-        <v>2</v>
-      </c>
       <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6">
         <v>23</v>
       </c>
-      <c r="Q6">
-        <v>20</v>
-      </c>
       <c r="R6">
+        <v>20</v>
+      </c>
+      <c r="S6">
         <v>0</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45980</v>
       </c>
@@ -944,49 +966,52 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>6</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>21</v>
       </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
       <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
         <v>18</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>35</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>8.5</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>14</v>
       </c>
-      <c r="O7">
-        <v>2</v>
-      </c>
       <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7">
         <v>24</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>28</v>
       </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="W7" t="s">
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="X7" t="s">
         <v>22</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45981</v>
       </c>
@@ -1009,43 +1034,46 @@
         <v>2</v>
       </c>
       <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
         <v>7</v>
       </c>
-      <c r="I8">
-        <v>20</v>
-      </c>
       <c r="J8">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
         <v>23</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>28</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>9.5</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>15</v>
       </c>
-      <c r="O8">
-        <v>2</v>
-      </c>
       <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8">
         <v>27</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>23</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>0</v>
       </c>
-      <c r="X8">
+      <c r="Y8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45982</v>
       </c>
@@ -1065,46 +1093,49 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
         <v>8</v>
       </c>
-      <c r="I9">
-        <v>20</v>
-      </c>
       <c r="J9">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
         <v>29</v>
       </c>
-      <c r="L9">
-        <v>20</v>
-      </c>
       <c r="M9">
+        <v>20</v>
+      </c>
+      <c r="N9">
         <v>9.6999999999999993</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>15</v>
       </c>
-      <c r="O9">
-        <v>2</v>
-      </c>
       <c r="P9">
+        <v>2</v>
+      </c>
+      <c r="Q9">
         <v>23</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>24</v>
       </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="X9">
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45983</v>
       </c>
@@ -1124,43 +1155,46 @@
         <v>2</v>
       </c>
       <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
         <v>4</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>9</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>25</v>
       </c>
-      <c r="J10">
-        <v>3</v>
-      </c>
       <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
         <v>35</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>24</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>11.5</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>16</v>
       </c>
-      <c r="O10">
-        <v>2</v>
-      </c>
       <c r="P10">
+        <v>2</v>
+      </c>
+      <c r="Q10">
         <v>25</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>30</v>
       </c>
-      <c r="X10">
+      <c r="Y10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45984</v>
       </c>
@@ -1180,46 +1214,49 @@
         <v>2</v>
       </c>
       <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>10</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>25</v>
       </c>
-      <c r="J11">
-        <v>3</v>
-      </c>
       <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
         <v>36</v>
       </c>
-      <c r="L11">
-        <v>20</v>
-      </c>
       <c r="M11">
+        <v>20</v>
+      </c>
+      <c r="N11">
         <v>12</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>14</v>
       </c>
-      <c r="O11">
-        <v>2</v>
-      </c>
       <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11">
         <v>22</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>26</v>
       </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="X11">
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45994</v>
       </c>
@@ -1245,40 +1282,43 @@
         <v>1</v>
       </c>
       <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
         <v>22</v>
       </c>
-      <c r="J12">
-        <v>2</v>
-      </c>
       <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
         <v>24</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>33</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>10.5</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>14</v>
       </c>
-      <c r="O12">
-        <v>2</v>
-      </c>
       <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12">
         <v>22</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>27</v>
       </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="X12">
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45995</v>
       </c>
@@ -1298,46 +1338,49 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
         <v>25</v>
       </c>
-      <c r="J13">
-        <v>2</v>
-      </c>
       <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
         <v>22</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>35</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>10.6</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>14</v>
       </c>
-      <c r="O13">
-        <v>2</v>
-      </c>
       <c r="P13">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q13">
+        <v>20</v>
+      </c>
+      <c r="R13">
         <v>26</v>
       </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
-      <c r="X13">
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45996</v>
       </c>
@@ -1357,49 +1400,52 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
         <v>25</v>
       </c>
-      <c r="J14">
-        <v>2</v>
-      </c>
       <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
         <v>16</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>30</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>10.8</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>14</v>
       </c>
-      <c r="O14">
-        <v>2</v>
-      </c>
       <c r="P14">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q14">
+        <v>20</v>
+      </c>
+      <c r="R14">
         <v>25</v>
       </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
-      <c r="W14" t="s">
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="X14" t="s">
         <v>23</v>
       </c>
-      <c r="X14">
+      <c r="Y14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45997</v>
       </c>
@@ -1419,46 +1465,49 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>4</v>
       </c>
       <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15">
         <v>24</v>
       </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
       <c r="K15">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="L15">
         <v>33</v>
       </c>
       <c r="M15">
+        <v>33</v>
+      </c>
+      <c r="N15">
         <v>10.9</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>14</v>
       </c>
-      <c r="O15">
-        <v>2</v>
-      </c>
       <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15">
         <v>22</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>26</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>0</v>
       </c>
-      <c r="X15">
+      <c r="Y15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45998</v>
       </c>
@@ -1478,46 +1527,49 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>5</v>
       </c>
       <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
         <v>24</v>
       </c>
-      <c r="J16">
-        <v>2</v>
-      </c>
       <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
         <v>25</v>
       </c>
-      <c r="L16">
-        <v>20</v>
-      </c>
       <c r="M16">
+        <v>20</v>
+      </c>
+      <c r="N16">
         <v>10.8</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>14</v>
       </c>
-      <c r="O16">
-        <v>3</v>
-      </c>
       <c r="P16">
+        <v>3</v>
+      </c>
+      <c r="Q16">
         <v>35</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>30</v>
       </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="X16">
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46008</v>
       </c>
@@ -1537,43 +1589,46 @@
         <v>2</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
         <v>6</v>
       </c>
-      <c r="I17">
-        <v>20</v>
-      </c>
       <c r="J17">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
         <v>18</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>25</v>
       </c>
-      <c r="O17">
-        <v>2</v>
-      </c>
       <c r="P17">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Q17">
         <v>25</v>
       </c>
       <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17" t="s">
-        <v>20</v>
-      </c>
-      <c r="X17">
+        <v>25</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46009</v>
       </c>
@@ -1596,46 +1651,49 @@
         <v>2</v>
       </c>
       <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
         <v>7</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>18</v>
       </c>
-      <c r="J18">
-        <v>3</v>
-      </c>
       <c r="K18">
+        <v>3</v>
+      </c>
+      <c r="L18">
         <v>36</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>28</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>9</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>14</v>
       </c>
-      <c r="O18">
-        <v>3</v>
-      </c>
       <c r="P18">
+        <v>3</v>
+      </c>
+      <c r="Q18">
         <v>33</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>29</v>
       </c>
-      <c r="R18">
-        <v>1</v>
-      </c>
-      <c r="S18" t="s">
-        <v>20</v>
-      </c>
-      <c r="X18">
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46010</v>
       </c>
@@ -1655,49 +1713,52 @@
         <v>2</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
         <v>8</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>24</v>
       </c>
-      <c r="J19">
-        <v>3</v>
-      </c>
       <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
         <v>30</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>38</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>4</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>38</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>35</v>
       </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19" t="s">
-        <v>20</v>
-      </c>
-      <c r="V19" t="s">
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19" t="s">
         <v>20</v>
       </c>
       <c r="W19" t="s">
+        <v>20</v>
+      </c>
+      <c r="X19" t="s">
         <v>24</v>
       </c>
-      <c r="X19">
+      <c r="Y19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46011</v>
       </c>
@@ -1717,49 +1778,52 @@
         <v>2</v>
       </c>
       <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
         <v>4</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>9</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>25</v>
       </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
       <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
         <v>26</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>22</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>9.75</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>14</v>
       </c>
-      <c r="O20">
-        <v>3</v>
-      </c>
       <c r="P20">
+        <v>3</v>
+      </c>
+      <c r="Q20">
         <v>32</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>35</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>0</v>
       </c>
-      <c r="S20" t="s">
-        <v>20</v>
-      </c>
-      <c r="X20">
+      <c r="T20" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46012</v>
       </c>
@@ -1779,49 +1843,52 @@
         <v>2</v>
       </c>
       <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
         <v>5</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>10</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>19</v>
       </c>
-      <c r="J21">
-        <v>2</v>
-      </c>
       <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
         <v>22</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>27</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>10</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>15</v>
       </c>
-      <c r="O21">
-        <v>3</v>
-      </c>
       <c r="P21">
+        <v>3</v>
+      </c>
+      <c r="Q21">
         <v>34</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>32</v>
       </c>
-      <c r="R21">
-        <v>1</v>
-      </c>
-      <c r="S21" t="s">
-        <v>20</v>
-      </c>
-      <c r="X21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46022</v>
       </c>
@@ -1847,37 +1914,40 @@
         <v>1</v>
       </c>
       <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
         <v>22</v>
       </c>
-      <c r="J22">
-        <v>2</v>
-      </c>
       <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
         <v>22</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>30</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>10</v>
       </c>
-      <c r="O22">
-        <v>3</v>
-      </c>
       <c r="P22">
+        <v>3</v>
+      </c>
+      <c r="Q22">
         <v>33</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>22</v>
       </c>
-      <c r="R22">
-        <v>1</v>
-      </c>
-      <c r="X22">
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46023</v>
       </c>
@@ -1897,43 +1967,46 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>2</v>
       </c>
       <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
         <v>27</v>
       </c>
-      <c r="J23">
-        <v>3</v>
-      </c>
       <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
         <v>29</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>26</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>10.5</v>
       </c>
-      <c r="O23">
-        <v>2</v>
-      </c>
       <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="Q23">
         <v>24</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>25</v>
       </c>
-      <c r="R23">
-        <v>1</v>
-      </c>
-      <c r="X23">
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46024</v>
       </c>
@@ -1953,49 +2026,52 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>3</v>
       </c>
       <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24">
         <v>28</v>
       </c>
-      <c r="J24">
-        <v>3</v>
-      </c>
       <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="L24">
         <v>27</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>26</v>
       </c>
-      <c r="O24">
-        <v>2</v>
-      </c>
       <c r="P24">
+        <v>2</v>
+      </c>
+      <c r="Q24">
         <v>26</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>30</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>0</v>
       </c>
-      <c r="S24" t="s">
-        <v>20</v>
-      </c>
       <c r="T24" t="s">
         <v>20</v>
       </c>
       <c r="U24" t="s">
         <v>20</v>
       </c>
-      <c r="X24">
+      <c r="V24" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46025</v>
       </c>
@@ -2015,43 +2091,43 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>4</v>
       </c>
       <c r="I25">
+        <v>4</v>
+      </c>
+      <c r="J25">
         <v>25</v>
       </c>
-      <c r="J25">
-        <v>3</v>
-      </c>
       <c r="K25">
+        <v>3</v>
+      </c>
+      <c r="L25">
         <v>29</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>28</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>10</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>21</v>
       </c>
-      <c r="O25">
-        <v>3</v>
-      </c>
       <c r="P25">
+        <v>3</v>
+      </c>
+      <c r="Q25">
         <v>30</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>32</v>
       </c>
-      <c r="R25">
-        <v>1</v>
-      </c>
-      <c r="S25" t="s">
-        <v>20</v>
+      <c r="S25">
+        <v>1</v>
       </c>
       <c r="T25" t="s">
         <v>20</v>
@@ -2059,11 +2135,14 @@
       <c r="U25" t="s">
         <v>20</v>
       </c>
-      <c r="X25">
+      <c r="V25" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46026</v>
       </c>
@@ -2083,40 +2162,40 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>5</v>
       </c>
       <c r="I26">
+        <v>5</v>
+      </c>
+      <c r="J26">
         <v>24</v>
       </c>
-      <c r="J26">
-        <v>3</v>
-      </c>
       <c r="K26">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="L26">
         <v>30</v>
       </c>
-      <c r="N26">
+      <c r="M26">
+        <v>30</v>
+      </c>
+      <c r="O26">
         <v>21</v>
       </c>
-      <c r="O26">
-        <v>3</v>
-      </c>
       <c r="P26">
+        <v>3</v>
+      </c>
+      <c r="Q26">
         <v>33</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>29</v>
       </c>
-      <c r="R26">
-        <v>1</v>
-      </c>
-      <c r="S26" t="s">
-        <v>20</v>
+      <c r="S26">
+        <v>1</v>
       </c>
       <c r="T26" t="s">
         <v>20</v>
@@ -2124,11 +2203,14 @@
       <c r="U26" t="s">
         <v>20</v>
       </c>
-      <c r="X26">
+      <c r="V26" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46036</v>
       </c>
@@ -2148,49 +2230,52 @@
         <v>2</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
         <v>6</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>25</v>
       </c>
-      <c r="J27">
-        <v>3</v>
-      </c>
       <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
         <v>26</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>28</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>10.5</v>
       </c>
-      <c r="N27">
-        <v>20</v>
-      </c>
       <c r="O27">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P27">
+        <v>2</v>
+      </c>
+      <c r="Q27">
         <v>25</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>28</v>
       </c>
-      <c r="R27">
-        <v>1</v>
-      </c>
-      <c r="T27" t="s">
-        <v>20</v>
-      </c>
-      <c r="X27">
+      <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="U27" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46037</v>
       </c>
@@ -2213,46 +2298,49 @@
         <v>2</v>
       </c>
       <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
         <v>7</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>21</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>4</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>38</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>27</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>10</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>21</v>
       </c>
-      <c r="O28">
-        <v>3</v>
-      </c>
       <c r="P28">
+        <v>3</v>
+      </c>
+      <c r="Q28">
         <v>26</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>28</v>
       </c>
-      <c r="R28">
-        <v>1</v>
-      </c>
-      <c r="T28" t="s">
-        <v>20</v>
-      </c>
-      <c r="X28">
+      <c r="S28">
+        <v>1</v>
+      </c>
+      <c r="U28" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46038</v>
       </c>
@@ -2272,46 +2360,49 @@
         <v>2</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29">
         <v>8</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>23</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>4</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>36</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>26</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>21</v>
       </c>
-      <c r="O29">
-        <v>2</v>
-      </c>
       <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29">
         <v>23</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>26</v>
       </c>
-      <c r="R29">
-        <v>1</v>
-      </c>
-      <c r="T29" t="s">
-        <v>20</v>
-      </c>
-      <c r="X29">
+      <c r="S29">
+        <v>1</v>
+      </c>
+      <c r="U29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46039</v>
       </c>
@@ -2331,43 +2422,46 @@
         <v>2</v>
       </c>
       <c r="G30">
+        <v>2</v>
+      </c>
+      <c r="H30">
         <v>4</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>9</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>23</v>
       </c>
-      <c r="J30">
-        <v>3</v>
-      </c>
       <c r="K30">
+        <v>3</v>
+      </c>
+      <c r="L30">
         <v>33</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>22</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>9.5</v>
       </c>
-      <c r="O30">
-        <v>3</v>
-      </c>
       <c r="P30">
+        <v>3</v>
+      </c>
+      <c r="Q30">
         <v>26</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>28</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>0</v>
       </c>
-      <c r="X30">
+      <c r="Y30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46040</v>
       </c>
@@ -2387,43 +2481,46 @@
         <v>2</v>
       </c>
       <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31">
         <v>5</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>10</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>22</v>
       </c>
-      <c r="J31">
-        <v>3</v>
-      </c>
       <c r="K31">
+        <v>3</v>
+      </c>
+      <c r="L31">
         <v>29</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>30</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>10.5</v>
       </c>
-      <c r="O31">
-        <v>3</v>
-      </c>
       <c r="P31">
+        <v>3</v>
+      </c>
+      <c r="Q31">
         <v>30</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>29</v>
       </c>
-      <c r="R31">
-        <v>1</v>
-      </c>
-      <c r="X31">
+      <c r="S31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46050</v>
       </c>
@@ -2449,40 +2546,43 @@
         <v>1</v>
       </c>
       <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
         <v>31</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>5</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>50</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>30</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>19</v>
       </c>
-      <c r="O32">
-        <v>2</v>
-      </c>
       <c r="P32">
+        <v>2</v>
+      </c>
+      <c r="Q32">
         <v>24</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>28</v>
       </c>
-      <c r="R32">
-        <v>1</v>
-      </c>
-      <c r="S32" t="s">
-        <v>20</v>
-      </c>
-      <c r="X32">
+      <c r="S32">
+        <v>1</v>
+      </c>
+      <c r="T32" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46051</v>
       </c>
@@ -2502,46 +2602,49 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>2</v>
       </c>
       <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
         <v>27</v>
       </c>
-      <c r="J33">
-        <v>3</v>
-      </c>
       <c r="K33">
+        <v>3</v>
+      </c>
+      <c r="L33">
         <v>34</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>27</v>
       </c>
-      <c r="N33">
-        <v>20</v>
-      </c>
       <c r="O33">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="P33">
+        <v>3</v>
+      </c>
+      <c r="Q33">
         <v>28</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>30</v>
       </c>
-      <c r="R33">
-        <v>1</v>
-      </c>
-      <c r="S33" t="s">
-        <v>20</v>
-      </c>
-      <c r="X33">
+      <c r="S33">
+        <v>1</v>
+      </c>
+      <c r="T33" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46052</v>
       </c>
@@ -2561,52 +2664,55 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>3</v>
       </c>
       <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
         <v>35</v>
       </c>
-      <c r="J34">
-        <v>3</v>
-      </c>
       <c r="K34">
+        <v>3</v>
+      </c>
+      <c r="L34">
         <v>26</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>30</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>10</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>21</v>
       </c>
-      <c r="O34">
-        <v>3</v>
-      </c>
       <c r="P34">
+        <v>3</v>
+      </c>
+      <c r="Q34">
         <v>26</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>32</v>
       </c>
-      <c r="R34">
-        <v>1</v>
-      </c>
-      <c r="S34" t="s">
-        <v>20</v>
+      <c r="S34">
+        <v>1</v>
       </c>
       <c r="T34" t="s">
         <v>20</v>
       </c>
-      <c r="X34">
+      <c r="U34" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46053</v>
       </c>
@@ -2626,40 +2732,43 @@
         <v>1</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>4</v>
       </c>
       <c r="I35">
+        <v>4</v>
+      </c>
+      <c r="J35">
         <v>32</v>
       </c>
-      <c r="J35">
-        <v>3</v>
-      </c>
       <c r="K35">
+        <v>3</v>
+      </c>
+      <c r="L35">
         <v>34</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>29</v>
       </c>
-      <c r="O35">
-        <v>3</v>
-      </c>
       <c r="P35">
+        <v>3</v>
+      </c>
+      <c r="Q35">
         <v>28</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>35</v>
       </c>
-      <c r="R35">
-        <v>1</v>
-      </c>
-      <c r="X35">
+      <c r="S35">
+        <v>1</v>
+      </c>
+      <c r="Y35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46054</v>
       </c>
@@ -2679,46 +2788,49 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>5</v>
       </c>
       <c r="I36">
+        <v>5</v>
+      </c>
+      <c r="J36">
         <v>30</v>
       </c>
-      <c r="J36">
-        <v>3</v>
-      </c>
       <c r="K36">
+        <v>3</v>
+      </c>
+      <c r="L36">
         <v>29</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>24</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>10.75</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>21</v>
       </c>
-      <c r="O36">
-        <v>2</v>
-      </c>
       <c r="P36">
+        <v>2</v>
+      </c>
+      <c r="Q36">
         <v>22</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>33</v>
       </c>
-      <c r="R36">
-        <v>1</v>
-      </c>
-      <c r="X36">
+      <c r="S36">
+        <v>1</v>
+      </c>
+      <c r="Y36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46064</v>
       </c>
@@ -2738,46 +2850,49 @@
         <v>2</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
         <v>6</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>25</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>4</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>42</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>33</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>21</v>
       </c>
-      <c r="O37">
-        <v>3</v>
-      </c>
       <c r="P37">
+        <v>3</v>
+      </c>
+      <c r="Q37">
         <v>29</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>33</v>
       </c>
-      <c r="R37">
-        <v>1</v>
-      </c>
-      <c r="S37" t="s">
-        <v>20</v>
-      </c>
-      <c r="X37">
+      <c r="S37">
+        <v>1</v>
+      </c>
+      <c r="T37" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46065</v>
       </c>
@@ -2800,46 +2915,49 @@
         <v>2</v>
       </c>
       <c r="H38">
+        <v>2</v>
+      </c>
+      <c r="I38">
         <v>7</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>25</v>
       </c>
-      <c r="J38">
-        <v>3</v>
-      </c>
       <c r="K38">
+        <v>3</v>
+      </c>
+      <c r="L38">
         <v>33</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>24</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>9.75</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>21</v>
       </c>
-      <c r="O38">
-        <v>2</v>
-      </c>
       <c r="P38">
+        <v>2</v>
+      </c>
+      <c r="Q38">
         <v>24</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>29</v>
       </c>
-      <c r="R38">
-        <v>1</v>
-      </c>
-      <c r="S38" t="s">
-        <v>20</v>
-      </c>
-      <c r="X38">
+      <c r="S38">
+        <v>1</v>
+      </c>
+      <c r="T38" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46066</v>
       </c>
@@ -2859,40 +2977,43 @@
         <v>2</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
         <v>8</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>25</v>
       </c>
-      <c r="J39">
-        <v>2</v>
-      </c>
       <c r="K39">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L39">
         <v>22</v>
       </c>
-      <c r="O39">
-        <v>3</v>
+      <c r="M39">
+        <v>22</v>
       </c>
       <c r="P39">
+        <v>3</v>
+      </c>
+      <c r="Q39">
         <v>25</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <v>28</v>
       </c>
-      <c r="R39">
-        <v>1</v>
-      </c>
-      <c r="X39">
+      <c r="S39">
+        <v>1</v>
+      </c>
+      <c r="Y39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46067</v>
       </c>
@@ -2912,46 +3033,49 @@
         <v>2</v>
       </c>
       <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
         <v>4</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>9</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>21</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>4</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>36</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>32</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>21</v>
       </c>
-      <c r="O40">
-        <v>2</v>
-      </c>
       <c r="P40">
+        <v>2</v>
+      </c>
+      <c r="Q40">
         <v>22</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>28</v>
       </c>
-      <c r="R40">
-        <v>1</v>
-      </c>
-      <c r="S40" t="s">
-        <v>20</v>
-      </c>
-      <c r="X40">
+      <c r="S40">
+        <v>1</v>
+      </c>
+      <c r="T40" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46068</v>
       </c>
@@ -2971,65 +3095,68 @@
         <v>2</v>
       </c>
       <c r="G41">
+        <v>2</v>
+      </c>
+      <c r="H41">
         <v>5</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>10</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>22</v>
       </c>
-      <c r="J41">
-        <v>3</v>
-      </c>
       <c r="K41">
+        <v>3</v>
+      </c>
+      <c r="L41">
         <v>34</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>33</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>10.7</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>21</v>
       </c>
-      <c r="O41">
-        <v>3</v>
-      </c>
       <c r="P41">
+        <v>3</v>
+      </c>
+      <c r="Q41">
         <v>26</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>28</v>
       </c>
-      <c r="R41">
-        <v>1</v>
-      </c>
-      <c r="T41" t="s">
-        <v>20</v>
-      </c>
-      <c r="X41">
+      <c r="S41">
+        <v>1</v>
+      </c>
+      <c r="U41" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
     </row>
